--- a/sources/baek_step7.xlsx
+++ b/sources/baek_step7.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA119"/>
+  <dimension ref="A1:AB119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="119" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>b4fa422f-6e31-43b3-9759-5f45fdb658e0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>d4caf371-0d93-482e-8ce0-5b16ce0b8442</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>5c3b9b68-bb7c-40be-9ba3-1b91141f4581</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>bbec9741-22e4-4224-9e7f-de83e8e9de23</t>
         </is>
@@ -783,12 +789,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>eae65a62-f056-4b35-b8fe-68558144c085</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>228e10ef-f2db-4a18-988c-2d3d629faea2</t>
         </is>
@@ -850,12 +856,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>01bbf88b-1358-4a7a-a1e0-36404ea9b704</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>df49457f-cee3-438c-b793-7a4c7abf9c16</t>
         </is>
@@ -864,22 +870,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f+2+3 [~5]</t>
+          <t>f+2+3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>f+2+3 [~5]</t>
+          <t>f+2+3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Human Cannonball [Tag]</t>
+          <t>Human Cannonball</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Human Cannonball [Tag]</t>
+          <t>Human Cannonball</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -924,10 +930,15 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>976f26f0-1bdd-4428-bcb5-a2c4e037ec03</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>aee01c2e-9289-4e68-ae44-3dd25484d144</t>
         </is>
@@ -936,27 +947,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2+4 [~5]; 2+5 [~5]</t>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Snake Revenge [Tag]</t>
+          <t>Snake Revenge</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Snake Revenge [Tag]</t>
+          <t>Snake Revenge</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -984,12 +995,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1046,12 +1062,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1108,12 +1124,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1245,20 +1261,25 @@
       </c>
       <c r="X13" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y13" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1340,12 +1361,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>401618cb-a56d-4071-ad1f-7b1b9c618eab</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>c9027765-fd20-49e4-84ee-dfc338379cbd</t>
         </is>
@@ -1427,12 +1448,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>face4f0a-179c-4e82-aaf0-8ca4f55772ff</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>1c4788c0-535a-4786-a700-d816e87d7a75</t>
         </is>
@@ -1514,12 +1535,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>c2de90a1-f1e2-4e37-ba68-445b65876194</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>654f50d7-980d-4dba-8ae0-0b53fb68f8d9</t>
         </is>
@@ -1601,12 +1622,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>c6c8ca21-05ec-4237-bde3-dfe880e74162</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>021ab0c4-aaad-4bcc-aa59-b6983abdc331</t>
         </is>
@@ -1688,12 +1709,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>6f951fa3-7e02-4ec1-83a6-1f15e09148a1</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>3caa10a5-7263-41f3-ab8f-60b6fd4ed962</t>
         </is>
@@ -1775,12 +1796,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>ef3e6b40-5e58-461c-bc2b-bb9cbd6fbfe8</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>2face33c-fe67-4971-86b0-7a36e59c53db</t>
         </is>
@@ -1862,12 +1883,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>cd3e95df-44e4-41a4-abcd-4790a36eb431</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>7d0b1e86-ea72-4973-aadf-e32117afde8e</t>
         </is>
@@ -1949,12 +1970,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>26fff5d0-5e71-4945-b979-79e105cc00f1</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>5d475c0d-8eb0-4f07-9add-66b15d8a239a</t>
         </is>
@@ -2036,12 +2057,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>1d21cbc6-ce54-41d5-ad48-8bf1b2659362</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>30a5e836-b7ea-4f02-b8b9-d92402c9a1ea</t>
         </is>
@@ -2123,12 +2144,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>b438d474-7657-40c8-9d87-0cd1a58d390d</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>eae198ac-b011-42a2-b38c-3e315da8538b</t>
         </is>
@@ -2210,12 +2231,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0e1d574c-614f-4d1b-bcee-7805ccf9e928</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>4082af05-8c9c-4525-856b-26a6ca57af3b</t>
         </is>
@@ -2297,12 +2318,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>2f1ae2ce-3e0f-408c-ab9c-576adbc08416</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>173acaf3-9a47-4646-925f-1f2867ddaac2</t>
         </is>
@@ -2384,12 +2405,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>b40f5659-92f0-49a7-81bd-dcf32a1a7677</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>ee18b089-3824-453c-9214-0c2f10cae085</t>
         </is>
@@ -2471,12 +2492,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>c2eebf63-1644-4e7e-8346-5811278a1478</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>cdcc8ffb-92c6-442b-84bf-7c69080d8fc4</t>
         </is>
@@ -2558,12 +2579,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>232a6f2c-cf46-4338-8c99-a992b6d49efd</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>fce4786d-7259-420b-a9fd-46e4cc03ef05</t>
         </is>
@@ -2645,12 +2666,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>888bc59d-6587-48e3-83f0-e8db7507b6e8</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>b4842cae-7de9-4c8c-af61-493be9275be7</t>
         </is>
@@ -2732,12 +2753,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>e69581f1-58b2-4944-b7da-da6aaddb5c83</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>dae953b7-c945-4f1d-88b8-2afb069dd9f2</t>
         </is>
@@ -2819,12 +2840,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>bfbda121-81d3-4689-bde4-a37d530c342c</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>c5670d2b-7d62-4a14-a56a-fac56422afc8</t>
         </is>
@@ -2906,12 +2927,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>a1871233-85a5-4d2c-9314-0a9e1796bba5</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>5ba68b1b-10cf-450a-8b2c-d26435f3d962</t>
         </is>
@@ -2993,12 +3014,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>f50ebd44-3ef5-4adb-839b-174a0590ac63</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>1b5f477e-689d-41d2-a394-8eb0375f10e2</t>
         </is>
@@ -3080,12 +3101,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>3b2dfcf4-98d3-4276-b8a3-ad212576cd1c</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>bf8d091b-d90f-4ac8-a23f-ae6f238429bb</t>
         </is>
@@ -3167,12 +3188,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>43ac6e85-2a09-4e64-b0f5-96716075d188</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>19fd15d2-69f9-4e5d-ae97-21270fdc601e</t>
         </is>
@@ -3254,12 +3275,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>c9f0fa63-42f7-435f-8845-571ca05546d6</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>84b2ca7f-2500-42e5-b7f8-e5c2de6e24d4</t>
         </is>
@@ -3341,12 +3362,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>ed09cc5d-72a2-4413-86e2-7d60caec36c5</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>8b174cd3-83bb-4415-adea-30beee32c6d8</t>
         </is>
@@ -3478,20 +3499,25 @@
       </c>
       <c r="X40" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y40" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3588,12 +3614,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>fa371d32-e450-42ed-8ee6-ef0bac690505</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>a4876316-5f19-47ed-a6ce-d35476fe7982</t>
         </is>
@@ -3690,12 +3716,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>45bf0d8f-6505-4c57-9e72-16efb901d6bd</t>
         </is>
@@ -3787,17 +3813,17 @@
           <t>Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>39d5078c-5045-43d1-984a-2fc1bc5573d3</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>1f6cd18a-5c92-4d02-8d39-ef796a7f7c96</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
@@ -3806,22 +3832,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 3,4&lt;3 [~5]</t>
+          <t>– 3,4&lt;3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1,2,3,4&lt;3 [~5]</t>
+          <t>1,2,3,4&lt;3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>– Launching Rocket [Tag]</t>
+          <t>– Launching Rocket</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Double Punch – Launching Rocket [Tag]</t>
+          <t>Double Punch – Launching Rocket</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3891,15 +3917,20 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
           <t>91eb70af-ac7d-4343-adf1-d1ea48c30ff4</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>347f6c58-8ebd-4f08-8511-e7d4636dac89</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
@@ -3991,17 +4022,17 @@
           <t>CS</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>a29915be-4e5c-484c-8cca-5bbc9014be8d</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>a95e0bb7-d58b-4fe0-b985-30209a18d74b</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
@@ -4093,17 +4124,17 @@
           <t>MS RC</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>379b609d-2beb-4dcc-87d1-5e78498cc206</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>84cd3b46-ddea-4ff1-a77b-be12c32581f5</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
@@ -4200,17 +4231,17 @@
           <t>Stun on the last hit.; Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>f41fef9f-4c9e-473d-8021-337c2ce01a12</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>5d51f5f3-8dd5-4697-ad5d-a3c92a9240e5</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
@@ -4302,17 +4333,17 @@
           <t>JG CSc GB</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>312d80f2-4456-4d54-b71b-afdf922f3136</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>97c3215d-d3c6-4f88-b6c2-e1d1667bc817</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>b7fdbad5-a130-4c10-89fc-492737205ce8</t>
         </is>
@@ -4414,12 +4445,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>8c0ac1bf-c6dd-4476-b181-a7d2d53df6c6</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>9fada296-e2e2-4a0a-976d-5b61ff068ae7</t>
         </is>
@@ -4511,12 +4542,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>b17514be-62c9-487e-a1f6-082a7a821f31</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>f879803d-9f2f-4f36-9d1f-f720d8ec1465</t>
         </is>
@@ -4613,12 +4644,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>d2c6d4ab-5d3d-4b67-83fe-4ff27f94784b</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>a57a4086-93d4-48e0-807f-718ce6ef0fd0</t>
         </is>
@@ -4720,12 +4751,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>7f216478-8d68-4e14-a0d9-8e2571f9c23f</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>2be591a8-91e3-4e62-b9a1-5cef9e294950</t>
         </is>
@@ -4822,12 +4853,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>6f823663-b84d-4170-8021-cac631aaf945</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>038e253c-4a1e-4937-9218-798a4b61f219</t>
         </is>
@@ -4924,12 +4955,12 @@
           <t>KSc GB</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>76ddc6d2-ca93-4600-9d41-ee0050de1431</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>a8d693b4-337f-459a-9341-e24665bc4ebc</t>
         </is>
@@ -4938,22 +4969,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f,N,d,df+3 [~5]</t>
+          <t>f,N,d,df+3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>f,N,d,df+3 [~5]</t>
+          <t>f,N,d,df+3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wing Blade [Tag]</t>
+          <t>Wing Blade</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wing Blade [Tag]</t>
+          <t>Wing Blade</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5028,10 +5059,15 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>12d0118e-3883-4a9f-bee4-c3c317c523c5</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>72ac36ec-71e2-4e19-8b69-22cbda0fd602</t>
         </is>
@@ -5040,22 +5076,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3,4&lt;3 [~5]</t>
+          <t>3,4&lt;3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3,4&lt;3 [~5]</t>
+          <t>3,4&lt;3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Launching Rocket [Tag]</t>
+          <t>Launching Rocket</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Launching Rocket [Tag]</t>
+          <t>Launching Rocket</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5135,10 +5171,15 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>a660a05e-98a9-49b0-9e0a-7610fbcee10d</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>ad810cc3-32fc-4924-8472-1adafb7caf95</t>
         </is>
@@ -5240,12 +5281,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>20a83a7a-eb70-46d6-8acc-95dd5017b99f</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>766808a5-36d7-4448-8a48-8721cc1b9c3f</t>
         </is>
@@ -5347,12 +5388,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>ce59542a-7601-4e98-b002-91a2876bdb8f</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>3e8cf538-9025-4ecc-aaa4-71f6ca513a6f</t>
         </is>
@@ -5454,12 +5495,12 @@
           <t>Stun on the last hit.; Going into Flamingo Stance cancels the last hit.; This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>65ddbdac-762e-457d-a52c-3bb4f27d6cfa</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>d9f86463-59e2-4226-abd8-b8e44bb76821</t>
         </is>
@@ -5561,12 +5602,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>bbe8646e-1aba-4c15-93b4-1c089a2b6969</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>91776ac7-5183-433f-9ea4-408c569a19c2</t>
         </is>
@@ -5658,12 +5699,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>7121fb66-bd0a-48e7-84ab-ed186c2fdca1</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>40f7e51c-2775-4a77-ad5f-7513cb912098</t>
         </is>
@@ -5760,12 +5801,12 @@
           <t>MS RC</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>e44f9bf0-691e-446e-9e59-3df093bdf1ed</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>4abcdc10-61cb-46d6-b42f-9e61dbec51dd</t>
         </is>
@@ -5867,12 +5908,12 @@
           <t>Stun on the last hit.; Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>2c2b3334-99a7-475e-b0b9-bebffc48cc17</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>effa8e88-223b-48b0-bf4e-9a24a4f4a6b9</t>
         </is>
@@ -5969,12 +6010,12 @@
           <t>JG GB CSc</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>ccb67edd-a198-4fbc-a5d4-5b9d858da0be</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>ad7488fc-00dd-4aab-8ce0-4de49aa48891</t>
         </is>
@@ -6036,12 +6077,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>3d7efa98-8878-4d06-b0ac-25b3f7ad0e3b</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>42048222-6e75-4088-865a-effb51efedbc</t>
         </is>
@@ -6133,12 +6174,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>33330bfd-6e00-4c7a-b125-70823a939422</t>
         </is>
@@ -6230,17 +6271,17 @@
           <t>-hh</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>56ceaacd-1e43-4098-8a67-7907c0b80ee3</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>cc2e24d5-cd47-42eb-b658-4620376d687a</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
@@ -6249,22 +6290,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>– 3,d+4&lt;3 [~5]</t>
+          <t>– 3,d+4&lt;3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>uf,N,3,d+4&lt;3 [~5]</t>
+          <t>uf,N,3,d+4&lt;3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>– Starlight Blade [Tag]</t>
+          <t>– Starlight Blade</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Baek Hop – Starlight Blade [Tag]</t>
+          <t>Baek Hop – Starlight Blade</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6339,15 +6380,20 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>710b21ba-fde1-42a8-b35d-61efbf09d507</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>c77327f3-4bbc-47e2-9886-81ebc7ed5939</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
@@ -6444,17 +6490,17 @@
           <t>CS</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>8e105078-1a8b-492a-9602-553f3c5a9a4a</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>ca7f409d-ebd7-4c5a-9303-00af2c23f050</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
@@ -6551,17 +6597,17 @@
           <t>MS RC</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>a2b3dfed-8572-4c46-bc34-204a87216bfd</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>236e98cf-c38f-4001-aecb-925ea54c70f6</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
@@ -6663,17 +6709,17 @@
           <t>Stun on the last hit.; Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>d02dc538-7fa1-47ba-a87f-b003c3f9f8a2</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>6296c065-977d-445a-a7a5-08d9eecd53b3</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
@@ -6770,17 +6816,17 @@
           <t>JG GB CSc</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>9cf7879d-2735-4c66-9ea4-c5c05eda0d63</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>8eb0f758-7a28-4d4e-97b1-0a6b39410478</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>8f21a266-decb-497a-bc17-95f7cc76af83</t>
         </is>
@@ -6887,12 +6933,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>4229fce5-7039-4d82-b966-5a9a96600f38</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>e4bd3998-584c-45c9-a2e3-5a79702f0b91</t>
         </is>
@@ -6901,27 +6947,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FC+3,3,N+3 [~5]</t>
+          <t>FC+3,3,N+3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FC+3,3,N+3 [~5]</t>
+          <t>FC+3,3,N+3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>d+3,3,N+3 [~5]</t>
+          <t>d+3,3,N+3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Snake Blade [Tag]</t>
+          <t>Snake Blade</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Snake Blade [Tag]</t>
+          <t>Snake Blade</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7001,10 +7047,15 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
           <t>f93ff29f-d3be-4c3e-805a-a931a61c99b7</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>e8388539-1b7d-449c-b763-c1d6f893a2f9</t>
         </is>
@@ -7061,12 +7112,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>6d265efa-9305-4292-9deb-8d59ec0f6cfc</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>57d8a375-78d0-4930-ab46-f848a5bee351</t>
         </is>
@@ -7163,12 +7214,12 @@
           <t>The 2nd hit only executes if the 1st hit connects or is blocked. If the 2nd hit is blocked, the 3rd hit is cancelled.</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>5789aab2-c659-4688-a3fd-5ac0d9ff2e26</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>616d237f-6781-4550-a3e2-0585ecce8bf9</t>
         </is>
@@ -7270,12 +7321,12 @@
           <t>This move can be done out of Flamingo.; The u/f+3+4 version can be done out of a FC and is also a little faster.</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>42ec062b-f6bf-461e-8847-fc894c0b3ed5</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>b58def04-4b74-43ca-83e0-ddd7ce001aad</t>
         </is>
@@ -7367,12 +7418,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>9ab59952-b42d-48c1-9f6b-51a30f2773b5</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>c9a95f17-846c-4521-954a-fe7d4fc38a85</t>
         </is>
@@ -7474,12 +7525,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>582e12b4-99d2-475f-a86d-b4f9c2f6f5cc</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>86f9ec72-b6e6-4bde-b37b-ae4ff267c695</t>
         </is>
@@ -7581,12 +7632,12 @@
           <t>Causes SLD on CH and KS on a crouching opponent</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>9f10aa65-b681-4eb9-98e2-3cf4eb5134f2</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>2ce18788-0144-4f94-b8f3-6a98dbd95c5a</t>
         </is>
@@ -7688,12 +7739,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>fb0236d2-65da-4ab2-81ba-a01d332600d6</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>78189463-680c-4543-bc06-22fbcad4e90d</t>
         </is>
@@ -7795,12 +7846,12 @@
           <t>Stun on the last hit.; Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>e917fbb5-b0df-4f3c-84c5-dbfd0a53d67d</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>2d67488a-8858-4221-897c-dda7132bfcc4</t>
         </is>
@@ -7897,12 +7948,12 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>8e2602ed-bd50-45de-9fb0-ed18b9b699b7</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>d852dead-945e-472e-ae74-8775744953c5</t>
         </is>
@@ -8004,12 +8055,12 @@
           <t>Stun on the last hit.; Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>ed571bf6-bc3b-4c92-b25b-29fc2afdc4b9</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>9eedb28c-7e45-40a9-a388-7dbf59b4a614</t>
         </is>
@@ -8106,12 +8157,12 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>6d2e2bfb-f5d1-4066-abb5-d54d3efbe672</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>17c1a1e8-05b7-4f4b-aec1-225c4d8a8f42</t>
         </is>
@@ -8208,12 +8259,12 @@
           <t>Going into Flamingo Stance cancels the last hit.; This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>03fbf9ce-64e4-44bb-bd8f-407890ad6887</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>2899e7bd-74b8-4995-82f8-d1028bb8813f</t>
         </is>
@@ -8315,12 +8366,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>ad3a089d-a205-42e1-b103-74b53d64e656</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>c63cc646-4394-41e2-abb9-8958be497954</t>
         </is>
@@ -8422,12 +8473,12 @@
           <t>Going into Flamingo Stance cancels the last hit.; This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>aaf7ad1e-8140-4ab5-a9c8-b114edebebf1</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>e73b1cde-d602-4183-add5-0437ceabe44d</t>
         </is>
@@ -8529,12 +8580,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>0a819bb9-9c9d-40bc-a909-c3dbdfd2d052</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>79b87e65-01eb-475d-a8f3-68961425a812</t>
         </is>
@@ -8591,12 +8642,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>f8b39f8b-aa0a-4f17-a05c-1da03b0ed0ac</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>e5f74648-babf-4557-ae76-cdb375d42721</t>
         </is>
@@ -8653,12 +8704,12 @@
           <t>This move can be done out of Flamingo.</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>5abeb8e1-894e-4fbc-8e4c-c044f37eb3d8</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>1037ee9d-6e1e-4fd3-be17-0f2c3b9d7701</t>
         </is>
@@ -8790,20 +8841,25 @@
       </c>
       <c r="X94" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y94" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y94" s="1" t="inlineStr">
+      <c r="Z94" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z94" s="1" t="inlineStr">
+      <c r="AA94" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA94" s="1" t="inlineStr">
+      <c r="AB94" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8860,12 +8916,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>a2b3cdff-fa07-44f9-b4bc-03d8e3b19f39</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>158d1c7a-e152-4d79-a25e-d7fba9c635e6</t>
         </is>
@@ -8922,12 +8978,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>f36735a7-cac0-424e-97ee-82d74c09705b</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>6ed323d3-a243-4596-86a1-f554478ec146</t>
         </is>
@@ -8989,12 +9045,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>571e96ff-325b-4c8a-8ec6-2887f7e46ab6</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>3c8de433-52df-4080-aff5-3f90952f76c4</t>
         </is>
@@ -9003,22 +9059,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2~3 [~5]</t>
+          <t>2~3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2~3 [~5]</t>
+          <t>2~3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Human Cannonball [Tag]</t>
+          <t>Human Cannonball</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Human Cannonball [Tag]</t>
+          <t>Human Cannonball</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9048,10 +9104,15 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
           <t>662add46-9258-494f-abea-ec1205818aee</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>7cd9150a-d4a3-48db-9793-be964e1c1658</t>
         </is>
@@ -9143,12 +9204,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>f4dba620-e606-4421-bcc2-484a8ace850b</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>8ff2e6a5-5455-4759-8503-86f19de9a58c</t>
         </is>
@@ -9245,12 +9306,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>e3046439-525d-4f35-8436-c7e4a1e65092</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>52d4ea0d-e01d-4cd3-b265-7a94301f0852</t>
         </is>
@@ -9347,12 +9408,12 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>30d21b7c-6734-4572-8e4f-f07abd652f59</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>38d092f2-e5b5-4337-9c3d-2623b642bb39</t>
         </is>
@@ -9449,12 +9510,12 @@
           <t>Going into Flamingo Stance cancels the last hit.</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>3a65dbc1-ca16-4e1c-914b-1a8529f4ba11</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>312a7afa-9e5a-448c-b531-c247bae493d9</t>
         </is>
@@ -9551,12 +9612,12 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>57215ee5-fcc4-41bd-9578-b9af2ac0497d</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>529f3844-54b9-4480-a7bd-7d4f2c35be9f</t>
         </is>
@@ -9565,22 +9626,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4,(release 3),4&lt;3 [~5]</t>
+          <t>4,(release 3),4&lt;3</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4,(release 3),4&lt;3 [~5]</t>
+          <t>4,(release 3),4&lt;3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Launching Rocket [Tag]</t>
+          <t>Launching Rocket</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Launching Rocket [Tag]</t>
+          <t>Launching Rocket</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9620,10 +9681,15 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
           <t>30e4e9ef-b70f-4830-8b96-fb68608c27d2</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>d4315da6-2010-4d49-bad2-3bede4ef94e0</t>
         </is>
@@ -9685,12 +9751,12 @@
           <t>lets assume you did F+1,2,3 to go into Flamingo and you are now holding Forward and Left Kick.</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>0663adbe-efcb-419d-9402-905d3982b3a1</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>30e35c4e-2f00-460c-8c4b-cfb7a1ed8754</t>
         </is>
@@ -9747,12 +9813,12 @@
           <t>lets assume you did F+1,2,3 to go into Flamingo and you are now holding Forward and Left Kick.</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>40aa667d-0dc7-43f8-b2a3-7787fbb240d5</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>3678e5fc-1bc1-45db-98da-a55e8baa67ff</t>
         </is>
@@ -9814,12 +9880,12 @@
           <t>lets assume you did F+1,2,3 to go into Flamingo and you are now holding Forward and Left Kick.</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>62f33a9a-10bb-475a-a386-ab631c6ab91c</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>f91c4c5d-143b-429e-bcc9-7dacef60c2a9</t>
         </is>
@@ -9828,22 +9894,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>d+4,(release 3),3,N+3 [~5]</t>
+          <t>d+4,(release 3),3,N+3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>d+4,(release 3),3,N+3 [~5]</t>
+          <t>d+4,(release 3),3,N+3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Snake Blade [Tag]</t>
+          <t>Snake Blade</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Snake Blade [Tag]</t>
+          <t>Snake Blade</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9883,10 +9949,15 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
           <t>693b8ead-d931-4c3f-8f52-f3db3f372654</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>39b3595a-21cc-4ef0-b62e-ac1a7f592ca2</t>
         </is>
@@ -9943,12 +10014,12 @@
           <t>lets assume you did F+1,2,3 to go into Flamingo and you are now holding Forward and Left Kick.</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>9fb5c8fb-d975-4a29-892e-d9d079dcf518</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>fddc8e18-382d-4b37-b10c-a33ee22539eb</t>
         </is>
@@ -10080,20 +10151,25 @@
       </c>
       <c r="X112" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y112" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y112" s="1" t="inlineStr">
+      <c r="Z112" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z112" s="1" t="inlineStr">
+      <c r="AA112" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA112" s="1" t="inlineStr">
+      <c r="AB112" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10175,12 +10251,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>89dc78f0-586d-4ce4-a5d5-65806732d201</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>e1892c8c-ed0d-422e-89ad-30ba390e9038</t>
         </is>
@@ -10247,17 +10323,17 @@
           <t>[!]-</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>5e2e7e20-9ec3-40fc-af2d-c113992b6bb6</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>e6bc26e9-2b87-4f22-a1fa-3b8f79fdf651</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>89dc78f0-586d-4ce4-a5d5-65806732d201</t>
         </is>
@@ -10389,20 +10465,25 @@
       </c>
       <c r="X117" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y117" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y117" s="1" t="inlineStr">
+      <c r="Z117" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z117" s="1" t="inlineStr">
+      <c r="AA117" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA117" s="1" t="inlineStr">
+      <c r="AB117" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10444,12 +10525,12 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
         </is>
       </c>
-      <c r="AA118" t="inlineStr">
+      <c r="AB118" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10491,12 +10572,12 @@
           <t>hhhlmmmlm[!]</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
-      <c r="AA119" t="inlineStr">
+      <c r="AB119" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/baek_step7.xlsx
+++ b/sources/baek_step7.xlsx
@@ -421,11 +421,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -437,7 +437,7 @@
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
@@ -3730,22 +3730,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>– 3 [~f_~b]</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1,2,3 [~f_~b]</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>– High Kick [FLA]</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Double Punch – High Kick [FLA]</t>
+          <t>Double Punch – High Kick</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4143,22 +4148,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1,2,3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>1,2,3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Double Punch – Black Widow [FLA]</t>
+          <t>Double Punch – Black Widow</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5402,22 +5412,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5815,22 +5830,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WS+3,4&lt;4,3 [~f_~b]</t>
+          <t>WS+3,4&lt;4,3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WS+3,4&lt;4,3 [~f_~b]</t>
+          <t>WS+3,4&lt;4,3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6616,22 +6636,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>uf,N,3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>uf,N,3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Baek Hop – Black Widow [FLA]</t>
+          <t>Baek Hop – Black Widow</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7228,27 +7253,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>uf+3+4 [f_b]</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7753,22 +7783,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>f+4&lt;3 [f_b]</t>
+          <t>f+4&lt;3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f+4&lt;3 [f_b]</t>
+          <t>f+4&lt;3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7962,22 +7997,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WS+4&lt;4&lt;3 [f_b]</t>
+          <t>WS+4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WS+4&lt;4&lt;3 [f_b]</t>
+          <t>WS+4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8171,22 +8211,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>df+4~4&lt;3 [f_b]</t>
+          <t>df+4~4&lt;3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>df+4~4&lt;3 [f_b]</t>
+          <t>df+4~4&lt;3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8380,27 +8425,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FC+4,3,3&lt;3 [f_b]</t>
+          <t>FC+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FC+4,3,3&lt;3 [f_b]</t>
+          <t>FC+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>d+4,3,3&lt;3 [f_b]</t>
+          <t>d+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8656,22 +8706,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>(~B)FLA</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9422,22 +9477,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3,4,4,3 [f_b]</t>
+          <t>3,4,4,3</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3,4,4,3 [f_b]</t>
+          <t>3,4,4,3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9765,22 +9825,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -10001,12 +10066,12 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -10243,12 +10308,12 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -10320,7 +10385,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -10564,12 +10629,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">

--- a/sources/baek_step7.xlsx
+++ b/sources/baek_step7.xlsx
@@ -1000,6 +1000,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
@@ -1062,6 +1067,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
@@ -1122,6 +1132,11 @@
       <c r="U10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -10590,6 +10605,11 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
+        </is>
+      </c>
       <c r="Z118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
@@ -10635,6 +10655,11 @@
       <c r="S119" t="inlineStr">
         <is>
           <t>hhhlmmmlm!</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
